--- a/1_sinif/bahar/Temel_Bilgi_Teknolojileri_II_Soru_Bankasi.xlsx
+++ b/1_sinif/bahar/Temel_Bilgi_Teknolojileri_II_Soru_Bankasi.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,56 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001B5E3A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00065F46"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007A5800"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009A3412"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00444444"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -82,48 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -655,7 +579,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sanal dünyalardaki eğim, gerçek hayaaki deneyimlerin ve etkileşimlerin yerini tutmayabilir.</t>
+          <t>Sanal dünyalardaki eğim, gerçek hayaaki deneyimlerin ve</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -665,12 +589,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sanal dünyalardaki uzaktan eğim, fiziksel sınıflarla kıyaslandığında daha maliyetli olabilir.</t>
+          <t>Sanal dünyalardaki uzaktan eğim, fiziksel sınıflarla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sanal dünyalarda öğrencilerin kişisel bilgileri ve öğrenme verileri, güvenliği garan edilmemiş veri depolama veya ağlar aracılığıyla tehlikeye alabilir. NAHTARI</t>
+          <t>Sanal dünyalarda öğrencilerin kişisel bilgileri ve öğrenme</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1115,7 +1039,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sanal dünyalar ark daha da yaygın olarak kullanılmaya başlandı ve çok sayıda sektör tarandan benimsenmeye başlandı.</t>
+          <t>Sanal dünyalar ark daha da yaygın olarak kullanılmaya ve çok</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1255,7 +1179,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Bilgisayar, cep telefonu ve diğer teknolojik araçların kullanımı konusunda yetkindirler.</t>
+          <t>Bilgisayar, cep telefonu ve diğer teknolojik araçların kullanımı</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1300,7 +1224,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Yaşam boyu öğrenenler teknolojik araçları ve kaynakları kullanarak öğrenmelerini desteklemelidir.</t>
+          <t>Yaşam boyu öğrenenler teknolojik araçları ve kaynakları</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1480,7 +1404,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>İş modellerini entegre etmek ve uyarlamak, nesnelerin internenin kuruluşlara faydalarındandır. interne” kavramının kısaltmasıdır. Bu kavram ilk olarak 1999 yılında İngiliz teknoloji uzmanı Kevin Ashton tarandan kullanılmışr</t>
+          <t>İş modellerini entegre etmek ve uyarlamak, nesnelerin</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1798,7 +1722,6 @@
           <t>Genel-Özel</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>🚫 İptal edilmiş soru</t>
@@ -1931,7 +1854,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Arama kutusuna “Çiçek and not Yapay” ifadesi yazıldığında yapay olan çiçeklerin bulunduğu sayfalar listelenir. ikinci kelimeyi bulundurmayan sayfaları aramak için kullanılır. Örneğin, arama kutusuna “Çiçek and not Yapay” ifadesi yazıldığında yapay olmayan çiçeklerin bulunduğu sayfalar listelenir.</t>
+          <t>Arama kutusuna “Çiçek and not Yapay” ifadesi yazıldığında</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2021,7 +1944,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Ağ topolojisi, ağı oluşturan bilgisayar ve cihazların fiziksel ve teorik olarak yerleşimleridir. bir adı da yıldız veri yolu topolojisidir. Bu topolojinin temel manğı yıldız ve veri yolu topolojilerini birleşrerek tek bir topoloji haline germesidir. Yani birbirinden bağımsız yıldız topolojileri bir veri yoluna bağlanarak tek topoloji haline gelmektedir. Örgü (Mesh) Topolojisi Örgü topolojisi ağda bulunan bütün bilgisayarın ve cihazların birbirine bağlı olduğu ve bağlanlardan biri kopsa bile çoğu veri pakenin doğru şekilde dağılmasını sağlayan bir topolojidir.</t>
+          <t>Ağ topolojisi, ağı oluşturan bilgisayar ve cihazların fiziksel ve</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2294,7 +2217,6 @@
           <t>Video listesi oluşturma</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>🚫 İptal edilmiş soru</t>
@@ -2427,10 +2349,9 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Küresel ve bölgesel siyasi ve ekonomik gelişmeler açısından dünyanın bilgi kaynağı olması</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>Küresel ve bölgesel siyasi ve ekonomik gelişmeler açısından</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>🚫 İptal edilmiş soru</t>
@@ -2608,7 +2529,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>İnternet ve dijital teknolojileri anlamaya, kullanmaya ve değerlendirmeye yönelik becerilerinizi gelişrin.</t>
+          <t>İnternet ve dijital teknolojileri anlamaya, kullanmaya ve</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3193,7 +3114,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sanal dünyada öğrencilerin kişisel bilgileri ve öğrenme verileri korunmalıdır. NAHTARI</t>
+          <t>Sanal dünyada öğrencilerin kişisel bilgileri ve öğrenme verileri</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3688,7 +3609,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bloglar, dinamik değildir. konular, görüşler, linkler sürekli değişebilir. Bir blog sitesine istenilen her şey gönderilebilir ancak bunun bütün sonuçlarından gönderici sorumlu olunur.</t>
+          <t>Bloglar, dinamik değildir.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4003,7 +3924,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Prova sekmesi görüntüleme ve provasını yapmaya dair ayarlar slayt gösterisi sekmesinde bulunur.</t>
+          <t>Prova sekmesi</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4048,7 +3969,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>I-www.atauni, II-hp://, III-tr, IV-edu sayfasına ulaşmak için adres sarına www.atauni.edu.tr internet adresi yazıldığında önceden tanımlanmış DNS sunucusu devreye girer ve URL adresini 194.27.49.80 nolu IP adresine dönüştürerek pake bu IP adresine yönlendirir. İnternet adresleri belli bir formata sahipr. Aşağıda hp://www.atauni.edu.tr/sinavlar/2011.html adresinin çözümlemesi yer almaktadır. (Tablo 11.2.) Tablo 11.2. İnternet Adresinin Çözümlemesi URL Bölüm adı Açıklama hp:// Transfer Protocol Adresin ilk bölümü protokol olarak adlandırılır. Bu uygulama protokolü istemci tarayıcıya dosyayı nasıl açacağını belirr. İnternet kullanıcıları çoğunlukla hp (Hypertext Transfer www.atauni Sunucu Adı Bilgilerin ya da dosyanın istendiği sunucu adıdır. Adresin sahibi tarandan belirlenir ve genellikle kurumu çağrışracak harlanması kolay bir isim kullanılır. edu Üst Seviye Alan adı (Top Level Domain gTLD) Alana sahip olan kuruluşun türünü belirr. Bu alanda karşılaşılan diğer kod ve açıklamaları aşağıdaki gibidir. com cari kuruluşlar (commercial) edu eğim kuruluşları (educaon) gov devlet kuruluşları (government) org cari olmayan kâr amacı gütmeyen kuruluşlar mil askeri kuruluşlar (military) net ağ organizasyonları (network) tr Ülke Kodu (Country Top Level Domain Sitenin yayınlandığı ülkeyi belirr.</t>
+          <t>I-www.atauni, II-hp://, III-tr, IV-edu</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4093,7 +4014,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>II ve III veri tabanı içerisinde kullanıcı ara birimi oluşturmak amacıyla kullanılan nesnelerdir. Formlar, tablolara bilgi girişini kolaylaşran ve daha anlaşılır bir ekran görüntüsü ile çalışmayı sağlayan nesnelerdir. Etkili bir form, veri tabanının kullanımını işlevsel hâle gerir.</t>
+          <t>II ve III</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4183,7 +4104,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>I, II ve III sunum modunda görüntülemek için kullanılır.</t>
+          <t>I, II ve III</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4903,7 +4824,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Tasarım görüntüleneceğini belirleyen animasyonları içeren animasyon grubu giriş kategorisidir.</t>
+          <t>Tasarım</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4948,7 +4869,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Vurgu esnasında nasıl görüntüleneceğini belirleyen animasyonları içerir.</t>
+          <t>Vurgu</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5218,7 +5139,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Yazdır görüntüleneceğini görmek için önizleme seçeneği kullanılabilir.</t>
+          <t>Yazdır</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5803,7 +5724,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Hp, sunucu ve istemci arasındaki mesajların yapısını ve mesaj alışverişlerinin nasıl yapılacağını belirler. sayfalarını görüntüleyen programlardır. Internet Explorer, Firefox, Chrome ve Opera gibi programlar web sayfalarında gezin için kullanılan tarayıcılardır.</t>
+          <t>Hp, sunucu ve istemci arasındaki mesajların yapısını ve</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5983,7 +5904,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Tasarım sekmesinden Oluştur varolan kayıtlardan seçme sorgusu yapılacakr. personelAdi “Ahmet” olan kayıtlar görüntüleneceği için ölçüt kısmına “Ahmet” yazılır. Tasarım sekmesinden Çalışr seçeneği kullanılarak kayıtlara ulaşılır.</t>
+          <t>Tasarım sekmesinden Oluştur</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6121,7 +6042,6 @@
           <t>İnternet paketleri dinamik bir yol izlemektedir. CEVAP AN</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>🚫 İptal edilmiş soru</t>
@@ -6164,7 +6084,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>İnternet tehditlerinden korunmak için kolayca tahmin edilmeyecek güçlü şifreler kullanılmalıdır. casus yazılımlarla kişisel bilgilerin çalınma riski vardır.</t>
+          <t>İnternet tehditlerinden korunmak için kolayca tahmin</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">

--- a/1_sinif/bahar/Temel_Bilgi_Teknolojileri_II_Soru_Bankasi.xlsx
+++ b/1_sinif/bahar/Temel_Bilgi_Teknolojileri_II_Soru_Bankasi.xlsx
@@ -512,6 +512,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -557,6 +558,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -602,6 +604,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -647,6 +650,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -692,6 +696,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -737,6 +742,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -774,7 +780,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Truva A NAHTARI</t>
+          <t>Truva A</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -782,6 +788,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -827,6 +834,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -872,6 +880,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -917,6 +926,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -962,6 +972,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1007,6 +1018,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1052,6 +1064,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1097,6 +1110,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1142,6 +1156,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1187,6 +1202,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1232,6 +1248,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1277,6 +1294,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1314,7 +1332,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4,5 Trilyon NAHTARI</t>
+          <t>4,5 Trilyon</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1322,6 +1340,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1367,6 +1386,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1412,6 +1432,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1449,7 +1470,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Word CEVAP AN</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1457,6 +1478,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1502,6 +1524,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1539,7 +1562,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>İnternet NAHTARI</t>
+          <t>İnternet</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1547,6 +1570,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1592,6 +1616,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1637,6 +1662,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1682,6 +1708,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1722,6 +1749,7 @@
           <t>Genel-Özel</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>🚫 İptal edilmiş soru</t>
@@ -1772,6 +1800,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1817,6 +1846,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1862,6 +1892,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1907,6 +1938,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1952,6 +1984,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1997,6 +2030,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2042,6 +2076,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2087,6 +2122,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2132,6 +2168,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2177,6 +2214,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2217,6 +2255,7 @@
           <t>Video listesi oluşturma</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>🚫 İptal edilmiş soru</t>
@@ -2267,6 +2306,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2312,6 +2352,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2352,6 +2393,7 @@
           <t>Küresel ve bölgesel siyasi ve ekonomik gelişmeler açısından</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>🚫 İptal edilmiş soru</t>
@@ -2402,6 +2444,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2447,6 +2490,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2492,6 +2536,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2537,6 +2582,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2582,6 +2628,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2627,6 +2674,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2672,6 +2720,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2717,6 +2766,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2762,6 +2812,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2807,6 +2858,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2852,6 +2904,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2897,6 +2950,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2942,6 +2996,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2987,6 +3042,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3032,6 +3088,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3077,6 +3134,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3122,6 +3180,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3167,6 +3226,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3204,7 +3264,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Akıllı telefon CEVAP AN</t>
+          <t>Akıllı telefon</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3212,6 +3272,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3257,6 +3318,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3302,6 +3364,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3347,6 +3410,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3392,6 +3456,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3437,6 +3502,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3482,6 +3548,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3527,6 +3594,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3572,6 +3640,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3617,6 +3686,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3654,7 +3724,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Dos CEVAP AN</t>
+          <t>Dos</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3662,6 +3732,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3707,6 +3778,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3752,6 +3824,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3797,6 +3870,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3842,6 +3916,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3887,6 +3962,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3932,6 +4008,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3977,6 +4054,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4022,6 +4100,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4067,6 +4146,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4112,6 +4192,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4157,6 +4238,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4202,6 +4284,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4247,6 +4330,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4292,6 +4376,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4337,6 +4422,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4382,6 +4468,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -4427,6 +4514,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4472,6 +4560,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4517,6 +4606,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4562,6 +4652,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4607,6 +4698,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4652,6 +4744,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4697,6 +4790,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4734,7 +4828,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Animasyon boyacısı NAHTARI</t>
+          <t>Animasyon boyacısı</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4742,6 +4836,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4787,6 +4882,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4832,6 +4928,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4877,6 +4974,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4922,6 +5020,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4959,7 +5058,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Ağ virüsleri CEVAP AN</t>
+          <t>Ağ virüsleri</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4967,6 +5066,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -5012,6 +5112,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -5057,6 +5158,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -5102,6 +5204,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -5147,6 +5250,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -5192,6 +5296,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -5237,6 +5342,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -5282,6 +5388,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -5327,6 +5434,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -5372,6 +5480,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -5417,6 +5526,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -5462,6 +5572,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -5507,6 +5618,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -5552,6 +5664,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -5597,6 +5710,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -5642,6 +5756,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -5679,7 +5794,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Sosyal medya plaormları CEVAP AN</t>
+          <t>Sosyal medya plaormları</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5687,6 +5802,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -5732,6 +5848,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -5777,6 +5894,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -5814,7 +5932,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Yakınlaşrma ve sıçrayış hareket yolları alnda var olan sekmelerdir. NAHTARI</t>
+          <t>Yakınlaşrma ve sıçrayış hareket yolları alnda var olan sekmelerdir.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -5822,6 +5940,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -5867,6 +5986,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -5912,6 +6032,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -5949,7 +6070,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Web okuyucu CEVAP AN</t>
+          <t>Web okuyucu</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -5957,6 +6078,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -6002,6 +6124,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -6039,9 +6162,10 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>İnternet paketleri dinamik bir yol izlemektedir. CEVAP AN</t>
-        </is>
-      </c>
+          <t>İnternet paketleri dinamik bir yol izlemektedir.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>🚫 İptal edilmiş soru</t>
@@ -6092,6 +6216,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -6137,6 +6262,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -6182,6 +6308,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -6227,6 +6354,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -6272,6 +6400,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J130" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
